--- a/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>21647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66132</t>
+          <t>65318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78607</t>
+          <t>82248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59227</t>
+          <t>57732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61457</t>
+          <t>61126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65023</t>
+          <t>66550</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110252</t>
+          <t>110963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59464</t>
+          <t>58365</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27730</t>
+          <t>27844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>36607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>37279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39272</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68547</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35466</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>63594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72876</t>
+          <t>73978</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91799</t>
+          <t>90613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128225</t>
+          <t>128468</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44008</t>
+          <t>45113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36516</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73074</t>
+          <t>72531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51510</t>
+          <t>53386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39246</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>54797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33199</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>68997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99122</t>
+          <t>99872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87360</t>
+          <t>88473</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116722</t>
+          <t>116839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64063</t>
+          <t>62414</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85262</t>
+          <t>84048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>155134</t>
+          <t>157484</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194077</t>
+          <t>194364</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>21643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40211</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76658</t>
+          <t>76870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>55154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56254</t>
+          <t>55017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68684</t>
+          <t>69197</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37290</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54988</t>
+          <t>56231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>117271</t>
+          <t>118275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98775</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134331</t>
+          <t>133670</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85694</t>
+          <t>85880</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109765</t>
+          <t>110956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>193859</t>
+          <t>194120</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238012</t>
+          <t>237297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49958</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58039</t>
+          <t>57460</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69938</t>
+          <t>70002</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>99148</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31748</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42291</t>
+          <t>41627</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41864</t>
+          <t>42924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>66812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>20693</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>38910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47943</t>
+          <t>49085</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>73235</t>
+          <t>75550</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58196</t>
+          <t>58012</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78933</t>
+          <t>79764</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113017</t>
+          <t>113502</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145548</t>
+          <t>145042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79527</t>
+          <t>78989</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107839</t>
+          <t>108080</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>68320</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89182</t>
+          <t>89131</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>152948</t>
+          <t>155591</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>187813</t>
+          <t>190295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53527</t>
+          <t>52705</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>78181</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>41799</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>54072</t>
+          <t>55466</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79216</t>
+          <t>80320</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>38616</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41910</t>
+          <t>39493</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>110129</t>
+          <t>113623</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>326714</t>
+          <t>332658</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>135761</t>
+          <t>135913</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>429507</t>
+          <t>428803</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45703</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>65250</t>
+          <t>64925</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>116433</t>
+          <t>114564</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>176926</t>
+          <t>177240</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>86814</t>
+          <t>84862</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35445</t>
+          <t>35866</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>53086</t>
+          <t>51982</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>85598</t>
+          <t>86532</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>36385</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>87552</t>
+          <t>87411</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107256</t>
+          <t>107423</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>118054</t>
+          <t>118627</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>144445</t>
+          <t>144655</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>32048</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>49406</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>37119</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>53825</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>72687</t>
+          <t>72952</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>97184</t>
+          <t>96839</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>27572</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>45343</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>45107</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>92388</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>159074</t>
+          <t>155621</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>63278</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>166409</t>
+          <t>167890</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>266998</t>
+          <t>269705</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>253830</t>
+          <t>255865</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>320807</t>
+          <t>320243</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>435819</t>
+          <t>433599</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>881134</t>
+          <t>927840</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>712041</t>
+          <t>709056</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1289526</t>
+          <t>1349015</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>436103</t>
+          <t>439416</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>515582</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>275744</t>
+          <t>261939</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>502509</t>
+          <t>500321</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>687056</t>
+          <t>655904</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>987498</t>
+          <t>984342</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>217935</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>111900</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>224052</t>
+          <t>225418</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>287399</t>
+          <t>276518</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>423509</t>
+          <t>424557</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>160446</t>
+          <t>162978</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>110261</t>
+          <t>102194</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>205961</t>
+          <t>205036</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>228196</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>343288</t>
+          <t>346830</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41965</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>56207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82248</t>
+          <t>74884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38973</t>
+          <t>45300</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57732</t>
+          <t>64481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48605</t>
+          <t>59611</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36330</t>
+          <t>45338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61126</t>
+          <t>75092</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>87578</t>
+          <t>104911</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>83803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110963</t>
+          <t>129466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32386</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>39884</t>
+          <t>40586</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58365</t>
+          <t>60608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>30625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39071</t>
+          <t>42990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26385</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>44162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>121728</t>
+          <t>126211</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121728</t>
+          <t>126211</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121728</t>
+          <t>126211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104497</t>
+          <t>123893</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104497</t>
+          <t>123893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104497</t>
+          <t>123893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>226225</t>
+          <t>250104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>226225</t>
+          <t>250104</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>226225</t>
+          <t>250104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37072</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>32754</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37279</t>
+          <t>47078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>52488</t>
+          <t>70905</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>55812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69753</t>
+          <t>89625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63594</t>
+          <t>70363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>62869</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>49999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73978</t>
+          <t>75423</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>108682</t>
+          <t>116208</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90613</t>
+          <t>96979</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128468</t>
+          <t>138665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>29706</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36187</t>
+          <t>40585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56685</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72531</t>
+          <t>78543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>44502</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>30730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>62180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128935</t>
+          <t>147057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128935</t>
+          <t>147057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>128935</t>
+          <t>147057</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>171194</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>171194</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>171194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>278226</t>
+          <t>318251</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>278226</t>
+          <t>318251</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>278226</t>
+          <t>318251</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>23591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27479</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>41594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>43112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54797</t>
+          <t>70851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42066</t>
+          <t>53190</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33524</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>64325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>83087</t>
+          <t>108681</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68997</t>
+          <t>91710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99872</t>
+          <t>126677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>112244</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88473</t>
+          <t>97287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116839</t>
+          <t>128464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62414</t>
+          <t>69214</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84048</t>
+          <t>91581</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>175479</t>
+          <t>192848</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157484</t>
+          <t>171477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194364</t>
+          <t>214227</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30129</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>45891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>68863</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50095</t>
+          <t>55082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76870</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>36110</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>23997</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>42660</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55154</t>
+          <t>63780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>208904</t>
+          <t>241595</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>208904</t>
+          <t>241595</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>208904</t>
+          <t>241595</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>181606</t>
+          <t>207810</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181606</t>
+          <t>207810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181606</t>
+          <t>207810</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>390511</t>
+          <t>449404</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>390511</t>
+          <t>449404</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>390511</t>
+          <t>449404</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,22 +2806,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30739</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55017</t>
+          <t>58644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>53737</t>
+          <t>63284</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69197</t>
+          <t>80343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>51939</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36478</t>
+          <t>41872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56231</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>99592</t>
+          <t>115224</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118275</t>
+          <t>133257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116478</t>
+          <t>113611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>130122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>98302</t>
+          <t>103869</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85880</t>
+          <t>92921</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110956</t>
+          <t>117528</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>214780</t>
+          <t>217481</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>194120</t>
+          <t>197071</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>237297</t>
+          <t>237237</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>39820</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49049</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>47416</t>
+          <t>51451</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57460</t>
+          <t>63019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>84866</t>
+          <t>91272</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70002</t>
+          <t>77646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99148</t>
+          <t>110030</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>33121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33061</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>28377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42924</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66812</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>247574</t>
+          <t>268374</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>247574</t>
+          <t>268374</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>247574</t>
+          <t>268374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>495873</t>
+          <t>528366</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>495873</t>
+          <t>528366</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>495873</t>
+          <t>528366</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>29797</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>40697</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>69224</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>83883</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>74156</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58012</t>
+          <t>63504</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79764</t>
+          <t>85820</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>128972</t>
+          <t>143380</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>124697</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145042</t>
+          <t>160925</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>93247</t>
+          <t>98927</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78989</t>
+          <t>85168</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108080</t>
+          <t>115323</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>78525</t>
+          <t>88335</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>68320</t>
+          <t>77597</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89131</t>
+          <t>100200</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>171772</t>
+          <t>187262</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>155591</t>
+          <t>168879</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>190295</t>
+          <t>205653</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27868</t>
+          <t>32141</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>64874</t>
+          <t>72479</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52705</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78181</t>
+          <t>87164</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>42950</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>66953</t>
+          <t>72736</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55466</t>
+          <t>60061</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>80320</t>
+          <t>86649</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>238775</t>
+          <t>259926</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>238775</t>
+          <t>259926</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>238775</t>
+          <t>259926</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>245729</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>245729</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>245729</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>460910</t>
+          <t>505655</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>460910</t>
+          <t>505655</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>460910</t>
+          <t>505655</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>38616</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>24654</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>33245</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>44562</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>256899</t>
+          <t>57548</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>113623</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>332658</t>
+          <t>66975</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>290144</t>
+          <t>92801</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>135913</t>
+          <t>79982</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>428803</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>62748</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>52819</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>73835</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>47615</t>
+          <t>51816</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>43404</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>60917</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>114565</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>102353</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>177240</t>
+          <t>129439</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>27983</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>32863</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>27390</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>35052</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>55373</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>84862</t>
+          <t>66880</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>29270</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>39121</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>29931</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>48377</t>
+          <t>51621</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>41213</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>86532</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>147938</t>
+          <t>163425</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>147938</t>
+          <t>163425</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>147938</t>
+          <t>163425</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>364233</t>
+          <t>175589</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>364233</t>
+          <t>175589</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>364233</t>
+          <t>175589</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>512171</t>
+          <t>339014</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>512171</t>
+          <t>339014</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>512171</t>
+          <t>339014</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>26374</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>27525</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>46416</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>97422</t>
+          <t>104120</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>87411</t>
+          <t>92754</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107423</t>
+          <t>115191</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>131671</t>
+          <t>140723</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>118627</t>
+          <t>127724</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>144655</t>
+          <t>155041</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>40112</t>
+          <t>43507</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>32721</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>44257</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>39909</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>53939</t>
+          <t>57994</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>84370</t>
+          <t>91657</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>72952</t>
+          <t>79369</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>96839</t>
+          <t>104961</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>40437</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>31733</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>45035</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>36097</t>
+          <t>39375</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>49490</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>114445</t>
+          <t>124222</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>114445</t>
+          <t>124222</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>114445</t>
+          <t>124222</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>200889</t>
+          <t>217896</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>200889</t>
+          <t>217896</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>200889</t>
+          <t>217896</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>315334</t>
+          <t>342118</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>315334</t>
+          <t>342118</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>315334</t>
+          <t>342118</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>118610</t>
+          <t>113722</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>89377</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>155621</t>
+          <t>145069</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>105088</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>63278</t>
+          <t>100858</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>140174</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>223698</t>
+          <t>232178</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>200512</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>269705</t>
+          <t>266867</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>285861</t>
+          <t>337909</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>255865</t>
+          <t>307497</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>320243</t>
+          <t>376985</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>587670</t>
+          <t>438715</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>433599</t>
+          <t>407506</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>927840</t>
+          <t>467763</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>873531</t>
+          <t>776625</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>709056</t>
+          <t>732929</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1349015</t>
+          <t>825430</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>475019</t>
+          <t>505249</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>439416</t>
+          <t>468699</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>515582</t>
+          <t>542651</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>422483</t>
+          <t>455357</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>261939</t>
+          <t>426477</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>500321</t>
+          <t>484250</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>897502</t>
+          <t>960606</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>655904</t>
+          <t>912501</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>984342</t>
+          <t>1006880</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>191683</t>
+          <t>211138</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>217935</t>
+          <t>241575</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>185868</t>
+          <t>205796</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>111900</t>
+          <t>183257</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>225418</t>
+          <t>228537</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>377551</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>379491</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>424557</t>
+          <t>452488</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -5951,27 +5951,27 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>154408</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>117195</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>178212</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>169115</t>
+          <t>192161</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>102194</t>
+          <t>171088</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>205036</t>
+          <t>215672</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>306967</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>315136</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>377139</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
